--- a/artfynd/A 54055-2024 artfynd.xlsx
+++ b/artfynd/A 54055-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121753262</v>
+        <v>121753336</v>
       </c>
       <c r="B2" t="n">
-        <v>105218</v>
+        <v>94543</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531047</v>
+        <v>530987</v>
       </c>
       <c r="R2" t="n">
-        <v>6342945</v>
+        <v>6342935</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121753336</v>
+        <v>121753262</v>
       </c>
       <c r="B3" t="n">
-        <v>94525</v>
+        <v>105236</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530987</v>
+        <v>531047</v>
       </c>
       <c r="R3" t="n">
-        <v>6342935</v>
+        <v>6342945</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 54055-2024 artfynd.xlsx
+++ b/artfynd/A 54055-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121753336</v>
+        <v>121753262</v>
       </c>
       <c r="B2" t="n">
-        <v>94543</v>
+        <v>105238</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530987</v>
+        <v>531047</v>
       </c>
       <c r="R2" t="n">
-        <v>6342935</v>
+        <v>6342945</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121753262</v>
+        <v>121753336</v>
       </c>
       <c r="B3" t="n">
-        <v>105236</v>
+        <v>94545</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531047</v>
+        <v>530987</v>
       </c>
       <c r="R3" t="n">
-        <v>6342945</v>
+        <v>6342935</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 54055-2024 artfynd.xlsx
+++ b/artfynd/A 54055-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121753262</v>
+        <v>121753336</v>
       </c>
       <c r="B2" t="n">
-        <v>105238</v>
+        <v>94552</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531047</v>
+        <v>530987</v>
       </c>
       <c r="R2" t="n">
-        <v>6342945</v>
+        <v>6342935</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121753336</v>
+        <v>121753262</v>
       </c>
       <c r="B3" t="n">
-        <v>94545</v>
+        <v>105245</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530987</v>
+        <v>531047</v>
       </c>
       <c r="R3" t="n">
-        <v>6342935</v>
+        <v>6342945</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 54055-2024 artfynd.xlsx
+++ b/artfynd/A 54055-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121753336</v>
+        <v>121753262</v>
       </c>
       <c r="B2" t="n">
-        <v>94552</v>
+        <v>105254</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530987</v>
+        <v>531047</v>
       </c>
       <c r="R2" t="n">
-        <v>6342935</v>
+        <v>6342945</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121753262</v>
+        <v>121753336</v>
       </c>
       <c r="B3" t="n">
-        <v>105245</v>
+        <v>94561</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>531047</v>
+        <v>530987</v>
       </c>
       <c r="R3" t="n">
-        <v>6342945</v>
+        <v>6342935</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
